--- a/artfynd/A 56539-2025 artfynd.xlsx
+++ b/artfynd/A 56539-2025 artfynd.xlsx
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107337</v>
+        <v>130107302</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,34 +1472,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507084</v>
+        <v>507075</v>
       </c>
       <c r="R9" t="n">
-        <v>7032690</v>
+        <v>7032759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,6 +1555,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1563,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107302</v>
+        <v>130107337</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,42 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507075</v>
+        <v>507084</v>
       </c>
       <c r="R10" t="n">
-        <v>7032759</v>
+        <v>7032690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1671,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,31 +1682,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 56539-2025 artfynd.xlsx
+++ b/artfynd/A 56539-2025 artfynd.xlsx
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107330</v>
+        <v>130107335</v>
       </c>
       <c r="B7" t="n">
-        <v>91659</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,37 +1239,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507223</v>
+        <v>507088</v>
       </c>
       <c r="R7" t="n">
-        <v>7032791</v>
+        <v>7032634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1303,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,34 +1312,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1359,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107335</v>
+        <v>130107330</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>91661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,34 +1341,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507088</v>
+        <v>507223</v>
       </c>
       <c r="R8" t="n">
-        <v>7032634</v>
+        <v>7032791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,8 +1417,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 56539-2025 artfynd.xlsx
+++ b/artfynd/A 56539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107338</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130108113</v>
       </c>
       <c r="B3" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130107339</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>130107357</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130107336</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107335</v>
+        <v>130107330</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>91748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,34 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507088</v>
+        <v>507223</v>
       </c>
       <c r="R7" t="n">
-        <v>7032634</v>
+        <v>7032791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1306,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,8 +1315,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1330,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107330</v>
+        <v>130107335</v>
       </c>
       <c r="B8" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,37 +1370,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507223</v>
+        <v>507088</v>
       </c>
       <c r="R8" t="n">
-        <v>7032791</v>
+        <v>7032634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1434,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,34 +1443,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1464,7 +1464,7 @@
         <v>130107302</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130107337</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>130107340</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>130107333</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 56539-2025 artfynd.xlsx
+++ b/artfynd/A 56539-2025 artfynd.xlsx
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107330</v>
+        <v>130107335</v>
       </c>
       <c r="B7" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,37 +1239,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507223</v>
+        <v>507088</v>
       </c>
       <c r="R7" t="n">
-        <v>7032791</v>
+        <v>7032634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1303,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,34 +1312,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1359,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107335</v>
+        <v>130107330</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,34 +1341,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507088</v>
+        <v>507223</v>
       </c>
       <c r="R8" t="n">
-        <v>7032634</v>
+        <v>7032791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,8 +1417,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107302</v>
+        <v>130107337</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,42 +1472,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507075</v>
+        <v>507084</v>
       </c>
       <c r="R9" t="n">
-        <v>7032759</v>
+        <v>7032690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1536,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,31 +1547,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107337</v>
+        <v>130107302</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,34 +1574,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507084</v>
+        <v>507075</v>
       </c>
       <c r="R10" t="n">
-        <v>7032690</v>
+        <v>7032759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1646,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,6 +1657,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 56539-2025 artfynd.xlsx
+++ b/artfynd/A 56539-2025 artfynd.xlsx
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107335</v>
+        <v>130107330</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,34 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507088</v>
+        <v>507223</v>
       </c>
       <c r="R7" t="n">
-        <v>7032634</v>
+        <v>7032791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1306,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,8 +1315,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1330,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107330</v>
+        <v>130107335</v>
       </c>
       <c r="B8" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,37 +1370,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507223</v>
+        <v>507088</v>
       </c>
       <c r="R8" t="n">
-        <v>7032791</v>
+        <v>7032634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1434,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,34 +1443,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107337</v>
+        <v>130107302</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,34 +1472,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507084</v>
+        <v>507075</v>
       </c>
       <c r="R9" t="n">
-        <v>7032690</v>
+        <v>7032759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,6 +1555,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1563,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107302</v>
+        <v>130107337</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,42 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507075</v>
+        <v>507084</v>
       </c>
       <c r="R10" t="n">
-        <v>7032759</v>
+        <v>7032690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1671,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
+          <t>Rikligt på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,31 +1682,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 56539-2025 artfynd.xlsx
+++ b/artfynd/A 56539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107338</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130108113</v>
       </c>
       <c r="B3" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>130107339</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>130107357</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130107336</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107335</v>
+        <v>130107330</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,34 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507088</v>
+        <v>507223</v>
       </c>
       <c r="R7" t="n">
-        <v>7032634</v>
+        <v>7032791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1306,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,8 +1315,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1330,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107330</v>
+        <v>130107335</v>
       </c>
       <c r="B8" t="n">
-        <v>91748</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,37 +1370,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507223</v>
+        <v>507088</v>
       </c>
       <c r="R8" t="n">
-        <v>7032791</v>
+        <v>7032634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,7 +1434,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,34 +1443,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1464,7 +1464,7 @@
         <v>130107337</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>130107340</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>130107333</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
